--- a/docs/workbook-split/dateien/Daten.xlsx
+++ b/docs/workbook-split/dateien/Daten.xlsx
@@ -2916,6 +2916,8 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
+    <row r="87"/>
     <row r="88">
       <c r="C88" t="inlineStr">
         <is>
